--- a/output/xlsx/AdministradorAdicionaOperadorDeEcommerce--GT-.xlsx
+++ b/output/xlsx/AdministradorAdicionaOperadorDeEcommerce--GT-.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="408" uniqueCount="73">
   <si>
     <t xml:space="preserve">System: </t>
   </si>
@@ -38,7 +38,7 @@
     <t>Reduced (Greedy Heuristic - Transition Coverage)</t>
   </si>
   <si>
-    <t>Size: 10 test case(s)</t>
+    <t>Size: 11 test case(s)</t>
   </si>
   <si>
     <t xml:space="preserve">Creation Date: </t>
@@ -92,25 +92,19 @@
     <t>Actual Result</t>
   </si>
   <si>
-    <t>Administrador: abre tela inicial do sistema</t>
+    <t>Administrador: clica no opcao 'E-commerces' no menu principal</t>
   </si>
   <si>
     <t/>
   </si>
   <si>
-    <t>SYSTEM exibe tela inicial do sistema</t>
-  </si>
-  <si>
-    <t>Administrador: clica no opcao 'Ecommerces' no menu principal</t>
-  </si>
-  <si>
-    <t>SYSTEM exibe a tela com a lista de Ecommerces cadastrados no sistema</t>
-  </si>
-  <si>
-    <t>Administrador: clica em um dos Ecommerces listados</t>
-  </si>
-  <si>
-    <t>SYSTEM exibe tela com informacões de Ecommerce</t>
+    <t>SYSTEM exibe a tela com a lista de E-commerces cadastrados no sistema</t>
+  </si>
+  <si>
+    <t>Administrador: clica em um dos E-commerces listados</t>
+  </si>
+  <si>
+    <t>SYSTEM exibe tela com informacões de E-commerce</t>
   </si>
   <si>
     <t>Administrador: adiciona os dados do novo Operador na secao 'Operadores' e clica no botao 'Adicionar Operador'</t>
@@ -128,33 +122,45 @@
     <t>TC2</t>
   </si>
   <si>
-    <t>Alternative Flow 1: Volta para listagem de Ecommerce</t>
-  </si>
-  <si>
-    <t>Administrador: clica no botao 'Voltar'</t>
+    <t>Alternative Flow 1: Navega pelas paginas da lista</t>
+  </si>
+  <si>
+    <t>Administrador: procura o E-commerce navegando pelas paginas da lista</t>
   </si>
   <si>
     <t>TC3</t>
   </si>
   <si>
-    <t>Alternative Flow 2: Cancela registro de novo operador de Ecommerce</t>
-  </si>
-  <si>
-    <t>Administrador: clica no botao 'Cancelar' de registro de operador</t>
+    <t>Alternative Flow 2: Volta para listagem de Ecommerce</t>
+  </si>
+  <si>
+    <t>Administrador: clica no botao Voltar</t>
   </si>
   <si>
     <t>TC4</t>
   </si>
   <si>
-    <t>Alternative Flow 3: Volta para tela inicial do sistema</t>
-  </si>
-  <si>
-    <t>Administrador: clica no botao 'Voltar' do form de Ecommerce</t>
+    <t>Alternative Flow 3: Cancela registro de novo operador de Ecommerce</t>
+  </si>
+  <si>
+    <t>Administrador: clica no botao Cancelar de registro de operador</t>
   </si>
   <si>
     <t>TC5</t>
   </si>
   <si>
+    <t>Alternative Flow 3: Clica no botao voltar</t>
+  </si>
+  <si>
+    <t>Administrador: clica no botao voltar</t>
+  </si>
+  <si>
+    <t>SYSTEM exibe tela de Dashboard</t>
+  </si>
+  <si>
+    <t>TC6</t>
+  </si>
+  <si>
     <t>Exception Flow 1: Campos obrigatorios</t>
   </si>
   <si>
@@ -170,7 +176,7 @@
     <t>Flow interrupted due to exception / error</t>
   </si>
   <si>
-    <t>TC6</t>
+    <t>TC7</t>
   </si>
   <si>
     <t>Exception Flow 2: Nome de Usuario ja cadastrado</t>
@@ -182,7 +188,7 @@
     <t>Administrador: informa um novo Nome de Usuario e clica no botao de 'Adicionar Operador'</t>
   </si>
   <si>
-    <t>TC7</t>
+    <t>TC8</t>
   </si>
   <si>
     <t>Exception Flow 3: Email ja cadastrado</t>
@@ -194,7 +200,7 @@
     <t>Administrador: informa um novo Email e clica no botao de 'Adicionar Operador'</t>
   </si>
   <si>
-    <t>TC8</t>
+    <t>TC9</t>
   </si>
   <si>
     <t>Exception Flow 4: Email invalido</t>
@@ -203,7 +209,7 @@
     <t>Administrador: informa um novo Email valido e clica no botao de 'Adicionar Operador'</t>
   </si>
   <si>
-    <t>TC9</t>
+    <t>TC10</t>
   </si>
   <si>
     <t>Exception Flow 5: Cpf ja cadastrado</t>
@@ -215,7 +221,7 @@
     <t>Administrador: informa um novo Cpf e clica no botao de 'Adicionar Operador'</t>
   </si>
   <si>
-    <t>TC10</t>
+    <t>TC11</t>
   </si>
   <si>
     <t>Exception Flow 6: Senhas nao coincidem</t>
@@ -316,7 +322,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:F124"/>
+  <dimension ref="A1:F122"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="17.578125" customWidth="true" bestFit="true"/>
@@ -480,92 +486,92 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="n" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="B13" t="s" s="3">
+      <c r="A13" t="s" s="1">
         <v>33</v>
       </c>
-      <c r="C13" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D13" t="s" s="3">
+      <c r="B13" t="s" s="0">
         <v>34</v>
       </c>
-      <c r="E13" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F13" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s" s="1">
+    </row>
+    <row r="16">
+      <c r="A16" t="s" s="1">
+        <v>11</v>
+      </c>
+      <c r="B16" t="s" s="0">
         <v>35</v>
       </c>
-      <c r="B14" t="s" s="0">
-        <v>36</v>
+      <c r="C16" t="s" s="1">
+        <v>13</v>
+      </c>
+      <c r="E16" t="s" s="1">
+        <v>14</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="1">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B17" t="s" s="0">
-        <v>37</v>
-      </c>
-      <c r="C17" t="s" s="1">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="E17" t="s" s="1">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="1">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B18" t="s" s="0">
-        <v>38</v>
-      </c>
-      <c r="E18" t="s" s="1">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="s" s="1">
-        <v>18</v>
-      </c>
-      <c r="B19" t="s" s="0">
-        <v>19</v>
+      <c r="A19" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="C19" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="D19" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="E19" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="F19" t="s" s="2">
+        <v>25</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="B20" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="C20" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="D20" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="E20" t="s" s="2">
-        <v>24</v>
-      </c>
-      <c r="F20" t="s" s="2">
-        <v>25</v>
+      <c r="A20" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B20" t="s" s="3">
+        <v>26</v>
+      </c>
+      <c r="C20" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D20" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="E20" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F20" t="s" s="3">
+        <v>27</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n" s="4">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="B21" t="s" s="3">
-        <v>26</v>
+        <v>37</v>
       </c>
       <c r="C21" t="s" s="3">
         <v>27</v>
@@ -582,7 +588,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n" s="4">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="B22" t="s" s="3">
         <v>29</v>
@@ -602,7 +608,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n" s="4">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="B23" t="s" s="3">
         <v>31</v>
@@ -621,138 +627,138 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="n" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="B24" t="s" s="3">
-        <v>39</v>
-      </c>
-      <c r="C24" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D24" t="s" s="3">
-        <v>30</v>
-      </c>
-      <c r="E24" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F24" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="B25" t="s" s="3">
-        <v>31</v>
-      </c>
-      <c r="C25" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D25" t="s" s="3">
-        <v>32</v>
-      </c>
-      <c r="E25" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F25" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n" s="4">
-        <v>6.0</v>
-      </c>
-      <c r="B26" t="s" s="3">
+      <c r="A24" t="s" s="1">
         <v>33</v>
       </c>
-      <c r="C26" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D26" t="s" s="3">
+      <c r="B24" t="s" s="0">
         <v>34</v>
-      </c>
-      <c r="E26" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F26" t="s" s="3">
-        <v>27</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="s" s="1">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="B27" t="s" s="0">
-        <v>36</v>
+        <v>38</v>
+      </c>
+      <c r="C27" t="s" s="1">
+        <v>13</v>
+      </c>
+      <c r="E27" t="s" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="B28" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="E28" t="s" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="s" s="1">
+        <v>18</v>
+      </c>
+      <c r="B29" t="s" s="0">
+        <v>19</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="s" s="1">
-        <v>11</v>
-      </c>
-      <c r="B30" t="s" s="0">
+      <c r="A30" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="B30" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="C30" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="D30" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="E30" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="F30" t="s" s="2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B31" t="s" s="3">
+        <v>26</v>
+      </c>
+      <c r="C31" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D31" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="E31" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F31" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="B32" t="s" s="3">
         <v>40</v>
       </c>
-      <c r="C30" t="s" s="1">
-        <v>13</v>
-      </c>
-      <c r="E30" t="s" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="s" s="1">
-        <v>15</v>
-      </c>
-      <c r="B31" t="s" s="0">
-        <v>41</v>
-      </c>
-      <c r="E31" t="s" s="1">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="s" s="1">
-        <v>18</v>
-      </c>
-      <c r="B32" t="s" s="0">
-        <v>19</v>
+      <c r="C32" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D32" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="E32" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F32" t="s" s="3">
+        <v>27</v>
       </c>
     </row>
     <row r="33">
-      <c r="A33" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="B33" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="C33" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="D33" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="E33" t="s" s="2">
-        <v>24</v>
-      </c>
-      <c r="F33" t="s" s="2">
-        <v>25</v>
+      <c r="A33" t="n" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="B33" t="s" s="3">
+        <v>29</v>
+      </c>
+      <c r="C33" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D33" t="s" s="3">
+        <v>30</v>
+      </c>
+      <c r="E33" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F33" t="s" s="3">
+        <v>27</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n" s="4">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="B34" t="s" s="3">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="C34" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D34" t="s" s="3">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="E34" t="s" s="3">
         <v>27</v>
@@ -762,560 +768,481 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" t="n" s="4">
-        <v>2.0</v>
-      </c>
-      <c r="B35" t="s" s="3">
-        <v>29</v>
-      </c>
-      <c r="C35" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D35" t="s" s="3">
-        <v>30</v>
-      </c>
-      <c r="E35" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F35" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n" s="4">
-        <v>3.0</v>
-      </c>
-      <c r="B36" t="s" s="3">
-        <v>31</v>
-      </c>
-      <c r="C36" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D36" t="s" s="3">
-        <v>32</v>
-      </c>
-      <c r="E36" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F36" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="B37" t="s" s="3">
-        <v>42</v>
-      </c>
-      <c r="C37" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D37" t="s" s="3">
-        <v>32</v>
-      </c>
-      <c r="E37" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F37" t="s" s="3">
-        <v>27</v>
+      <c r="A35" t="s" s="1">
+        <v>33</v>
+      </c>
+      <c r="B35" t="s" s="0">
+        <v>34</v>
       </c>
     </row>
     <row r="38">
-      <c r="A38" t="n" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="B38" t="s" s="3">
-        <v>33</v>
-      </c>
-      <c r="C38" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D38" t="s" s="3">
-        <v>34</v>
-      </c>
-      <c r="E38" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F38" t="s" s="3">
-        <v>27</v>
+      <c r="A38" t="s" s="1">
+        <v>11</v>
+      </c>
+      <c r="B38" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="C38" t="s" s="1">
+        <v>13</v>
+      </c>
+      <c r="E38" t="s" s="1">
+        <v>14</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="s" s="1">
-        <v>35</v>
+        <v>15</v>
       </c>
       <c r="B39" t="s" s="0">
-        <v>36</v>
+        <v>42</v>
+      </c>
+      <c r="E39" t="s" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="s" s="1">
+        <v>18</v>
+      </c>
+      <c r="B40" t="s" s="0">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="B41" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="C41" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="D41" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="E41" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="F41" t="s" s="2">
+        <v>25</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" t="s" s="1">
+      <c r="A42" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B42" t="s" s="3">
+        <v>26</v>
+      </c>
+      <c r="C42" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D42" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="E42" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F42" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="B43" t="s" s="3">
+        <v>29</v>
+      </c>
+      <c r="C43" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D43" t="s" s="3">
+        <v>30</v>
+      </c>
+      <c r="E43" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F43" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="B44" t="s" s="3">
+        <v>43</v>
+      </c>
+      <c r="C44" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D44" t="s" s="3">
+        <v>30</v>
+      </c>
+      <c r="E44" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F44" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="B45" t="s" s="3">
+        <v>31</v>
+      </c>
+      <c r="C45" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D45" t="s" s="3">
+        <v>32</v>
+      </c>
+      <c r="E45" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F45" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="s" s="1">
+        <v>33</v>
+      </c>
+      <c r="B46" t="s" s="0">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="s" s="1">
         <v>11</v>
       </c>
-      <c r="B42" t="s" s="0">
-        <v>43</v>
-      </c>
-      <c r="C42" t="s" s="1">
+      <c r="B49" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="C49" t="s" s="1">
         <v>13</v>
       </c>
-      <c r="E42" t="s" s="1">
+      <c r="E49" t="s" s="1">
         <v>14</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="s" s="1">
+    <row r="50">
+      <c r="A50" t="s" s="1">
         <v>15</v>
       </c>
-      <c r="B43" t="s" s="0">
-        <v>44</v>
-      </c>
-      <c r="E43" t="s" s="1">
+      <c r="B50" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="E50" t="s" s="1">
         <v>17</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="s" s="1">
+    <row r="51">
+      <c r="A51" t="s" s="1">
         <v>18</v>
       </c>
-      <c r="B44" t="s" s="0">
+      <c r="B51" t="s" s="0">
         <v>19</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="s" s="2">
+    <row r="52">
+      <c r="A52" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="B45" t="s" s="2">
+      <c r="B52" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="C45" t="s" s="2">
+      <c r="C52" t="s" s="2">
         <v>22</v>
       </c>
-      <c r="D45" t="s" s="2">
+      <c r="D52" t="s" s="2">
         <v>23</v>
       </c>
-      <c r="E45" t="s" s="2">
+      <c r="E52" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="F45" t="s" s="2">
+      <c r="F52" t="s" s="2">
         <v>25</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="n" s="4">
+    <row r="53">
+      <c r="A53" t="n" s="4">
         <v>1.0</v>
       </c>
-      <c r="B46" t="s" s="3">
+      <c r="B53" t="s" s="3">
         <v>26</v>
       </c>
-      <c r="C46" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D46" t="s" s="3">
+      <c r="C53" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D53" t="s" s="3">
         <v>28</v>
       </c>
-      <c r="E46" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F46" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n" s="4">
+      <c r="E53" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F53" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n" s="4">
         <v>2.0</v>
       </c>
-      <c r="B47" t="s" s="3">
+      <c r="B54" t="s" s="3">
         <v>29</v>
       </c>
-      <c r="C47" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D47" t="s" s="3">
+      <c r="C54" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D54" t="s" s="3">
         <v>30</v>
       </c>
-      <c r="E47" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F47" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n" s="4">
+      <c r="E54" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F54" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n" s="4">
         <v>3.0</v>
       </c>
-      <c r="B48" t="s" s="3">
-        <v>45</v>
-      </c>
-      <c r="C48" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D48" t="s" s="3">
-        <v>28</v>
-      </c>
-      <c r="E48" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F48" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="B49" t="s" s="3">
-        <v>29</v>
-      </c>
-      <c r="C49" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D49" t="s" s="3">
-        <v>30</v>
-      </c>
-      <c r="E49" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F49" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="B50" t="s" s="3">
-        <v>31</v>
-      </c>
-      <c r="C50" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D50" t="s" s="3">
-        <v>32</v>
-      </c>
-      <c r="E50" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F50" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n" s="4">
-        <v>6.0</v>
-      </c>
-      <c r="B51" t="s" s="3">
-        <v>33</v>
-      </c>
-      <c r="C51" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D51" t="s" s="3">
-        <v>34</v>
-      </c>
-      <c r="E51" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F51" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="B52" t="s" s="0">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="s" s="1">
-        <v>11</v>
-      </c>
-      <c r="B55" t="s" s="0">
+      <c r="B55" t="s" s="3">
         <v>46</v>
       </c>
-      <c r="C55" t="s" s="1">
-        <v>13</v>
-      </c>
-      <c r="E55" t="s" s="1">
-        <v>14</v>
+      <c r="C55" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D55" t="s" s="3">
+        <v>47</v>
+      </c>
+      <c r="E55" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F55" t="s" s="3">
+        <v>27</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="1">
+        <v>33</v>
+      </c>
+      <c r="B56" t="s" s="0">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="s" s="1">
+        <v>11</v>
+      </c>
+      <c r="B59" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="C59" t="s" s="1">
+        <v>13</v>
+      </c>
+      <c r="E59" t="s" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="s" s="1">
         <v>15</v>
       </c>
-      <c r="B56" t="s" s="0">
-        <v>47</v>
-      </c>
-      <c r="E56" t="s" s="1">
+      <c r="B60" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="E60" t="s" s="1">
         <v>17</v>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="s" s="1">
+    <row r="61">
+      <c r="A61" t="s" s="1">
         <v>18</v>
       </c>
-      <c r="B57" t="s" s="0">
+      <c r="B61" t="s" s="0">
         <v>19</v>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="s" s="2">
+    <row r="62">
+      <c r="A62" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="B58" t="s" s="2">
+      <c r="B62" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="C58" t="s" s="2">
+      <c r="C62" t="s" s="2">
         <v>22</v>
       </c>
-      <c r="D58" t="s" s="2">
+      <c r="D62" t="s" s="2">
         <v>23</v>
       </c>
-      <c r="E58" t="s" s="2">
+      <c r="E62" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="F58" t="s" s="2">
+      <c r="F62" t="s" s="2">
         <v>25</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="n" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="B59" t="s" s="3">
-        <v>26</v>
-      </c>
-      <c r="C59" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D59" t="s" s="3">
-        <v>28</v>
-      </c>
-      <c r="E59" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F59" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="n" s="4">
-        <v>2.0</v>
-      </c>
-      <c r="B60" t="s" s="3">
-        <v>29</v>
-      </c>
-      <c r="C60" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D60" t="s" s="3">
-        <v>30</v>
-      </c>
-      <c r="E60" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F60" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="n" s="4">
-        <v>3.0</v>
-      </c>
-      <c r="B61" t="s" s="3">
-        <v>31</v>
-      </c>
-      <c r="C61" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D61" t="s" s="3">
-        <v>32</v>
-      </c>
-      <c r="E61" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F61" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="n" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="B62" t="s" s="3">
-        <v>33</v>
-      </c>
-      <c r="C62" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D62" t="s" s="3">
-        <v>48</v>
-      </c>
-      <c r="E62" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F62" t="s" s="3">
-        <v>27</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n" s="4">
-        <v>5.0</v>
+        <v>1.0</v>
       </c>
       <c r="B63" t="s" s="3">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="C63" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D63" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="E63" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F63" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="B64" t="s" s="3">
+        <v>29</v>
+      </c>
+      <c r="C64" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D64" t="s" s="3">
+        <v>30</v>
+      </c>
+      <c r="E64" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F64" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="B65" t="s" s="3">
+        <v>31</v>
+      </c>
+      <c r="C65" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D65" t="s" s="3">
         <v>50</v>
       </c>
-      <c r="E63" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F63" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="B64" t="s" s="0">
+      <c r="E65" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F65" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="B66" t="s" s="3">
         <v>51</v>
+      </c>
+      <c r="C66" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D66" t="s" s="3">
+        <v>52</v>
+      </c>
+      <c r="E66" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F66" t="s" s="3">
+        <v>27</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="s" s="1">
+        <v>33</v>
+      </c>
+      <c r="B67" t="s" s="0">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="s" s="1">
         <v>11</v>
       </c>
-      <c r="B67" t="s" s="0">
-        <v>52</v>
-      </c>
-      <c r="C67" t="s" s="1">
+      <c r="B70" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="C70" t="s" s="1">
         <v>13</v>
       </c>
-      <c r="E67" t="s" s="1">
+      <c r="E70" t="s" s="1">
         <v>14</v>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" t="s" s="1">
+    <row r="71">
+      <c r="A71" t="s" s="1">
         <v>15</v>
       </c>
-      <c r="B68" t="s" s="0">
-        <v>53</v>
-      </c>
-      <c r="E68" t="s" s="1">
+      <c r="B71" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="E71" t="s" s="1">
         <v>17</v>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" t="s" s="1">
+    <row r="72">
+      <c r="A72" t="s" s="1">
         <v>18</v>
       </c>
-      <c r="B69" t="s" s="0">
+      <c r="B72" t="s" s="0">
         <v>19</v>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" t="s" s="2">
+    <row r="73">
+      <c r="A73" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="B70" t="s" s="2">
+      <c r="B73" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="C70" t="s" s="2">
+      <c r="C73" t="s" s="2">
         <v>22</v>
       </c>
-      <c r="D70" t="s" s="2">
+      <c r="D73" t="s" s="2">
         <v>23</v>
       </c>
-      <c r="E70" t="s" s="2">
+      <c r="E73" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="F70" t="s" s="2">
+      <c r="F73" t="s" s="2">
         <v>25</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="n" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="B71" t="s" s="3">
-        <v>26</v>
-      </c>
-      <c r="C71" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D71" t="s" s="3">
-        <v>28</v>
-      </c>
-      <c r="E71" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F71" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="n" s="4">
-        <v>2.0</v>
-      </c>
-      <c r="B72" t="s" s="3">
-        <v>29</v>
-      </c>
-      <c r="C72" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D72" t="s" s="3">
-        <v>30</v>
-      </c>
-      <c r="E72" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F72" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="n" s="4">
-        <v>3.0</v>
-      </c>
-      <c r="B73" t="s" s="3">
-        <v>31</v>
-      </c>
-      <c r="C73" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D73" t="s" s="3">
-        <v>32</v>
-      </c>
-      <c r="E73" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F73" t="s" s="3">
-        <v>27</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n" s="4">
-        <v>4.0</v>
+        <v>1.0</v>
       </c>
       <c r="B74" t="s" s="3">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="C74" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D74" t="s" s="3">
-        <v>54</v>
+        <v>28</v>
       </c>
       <c r="E74" t="s" s="3">
         <v>27</v>
@@ -1326,16 +1253,16 @@
     </row>
     <row r="75">
       <c r="A75" t="n" s="4">
-        <v>5.0</v>
+        <v>2.0</v>
       </c>
       <c r="B75" t="s" s="3">
-        <v>55</v>
+        <v>29</v>
       </c>
       <c r="C75" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D75" t="s" s="3">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="E75" t="s" s="3">
         <v>27</v>
@@ -1345,118 +1272,118 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="B76" t="s" s="0">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="s" s="1">
-        <v>11</v>
-      </c>
-      <c r="B79" t="s" s="0">
+      <c r="A76" t="n" s="4">
+        <v>3.0</v>
+      </c>
+      <c r="B76" t="s" s="3">
+        <v>31</v>
+      </c>
+      <c r="C76" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D76" t="s" s="3">
         <v>56</v>
       </c>
-      <c r="C79" t="s" s="1">
-        <v>13</v>
-      </c>
-      <c r="E79" t="s" s="1">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="s" s="1">
-        <v>15</v>
-      </c>
-      <c r="B80" t="s" s="0">
+      <c r="E76" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F76" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="B77" t="s" s="3">
         <v>57</v>
       </c>
-      <c r="E80" t="s" s="1">
-        <v>17</v>
+      <c r="C77" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D77" t="s" s="3">
+        <v>52</v>
+      </c>
+      <c r="E77" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F77" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s" s="1">
+        <v>33</v>
+      </c>
+      <c r="B78" t="s" s="0">
+        <v>53</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="1">
+        <v>11</v>
+      </c>
+      <c r="B81" t="s" s="0">
+        <v>58</v>
+      </c>
+      <c r="C81" t="s" s="1">
+        <v>13</v>
+      </c>
+      <c r="E81" t="s" s="1">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="B82" t="s" s="0">
+        <v>59</v>
+      </c>
+      <c r="E82" t="s" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="1">
         <v>18</v>
       </c>
-      <c r="B81" t="s" s="0">
+      <c r="B83" t="s" s="0">
         <v>19</v>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" t="s" s="2">
+    <row r="84">
+      <c r="A84" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="B82" t="s" s="2">
+      <c r="B84" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="C82" t="s" s="2">
+      <c r="C84" t="s" s="2">
         <v>22</v>
       </c>
-      <c r="D82" t="s" s="2">
+      <c r="D84" t="s" s="2">
         <v>23</v>
       </c>
-      <c r="E82" t="s" s="2">
+      <c r="E84" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="F82" t="s" s="2">
+      <c r="F84" t="s" s="2">
         <v>25</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="n" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="B83" t="s" s="3">
-        <v>26</v>
-      </c>
-      <c r="C83" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D83" t="s" s="3">
-        <v>28</v>
-      </c>
-      <c r="E83" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F83" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="n" s="4">
-        <v>2.0</v>
-      </c>
-      <c r="B84" t="s" s="3">
-        <v>29</v>
-      </c>
-      <c r="C84" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D84" t="s" s="3">
-        <v>30</v>
-      </c>
-      <c r="E84" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F84" t="s" s="3">
-        <v>27</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n" s="4">
-        <v>3.0</v>
+        <v>1.0</v>
       </c>
       <c r="B85" t="s" s="3">
-        <v>31</v>
+        <v>26</v>
       </c>
       <c r="C85" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D85" t="s" s="3">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E85" t="s" s="3">
         <v>27</v>
@@ -1467,16 +1394,16 @@
     </row>
     <row r="86">
       <c r="A86" t="n" s="4">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="B86" t="s" s="3">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="C86" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D86" t="s" s="3">
-        <v>58</v>
+        <v>30</v>
       </c>
       <c r="E86" t="s" s="3">
         <v>27</v>
@@ -1487,16 +1414,16 @@
     </row>
     <row r="87">
       <c r="A87" t="n" s="4">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="B87" t="s" s="3">
-        <v>59</v>
+        <v>31</v>
       </c>
       <c r="C87" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D87" t="s" s="3">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="E87" t="s" s="3">
         <v>27</v>
@@ -1506,98 +1433,98 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="B88" t="s" s="0">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="s" s="1">
-        <v>11</v>
-      </c>
-      <c r="B91" t="s" s="0">
-        <v>60</v>
-      </c>
-      <c r="C91" t="s" s="1">
-        <v>13</v>
-      </c>
-      <c r="E91" t="s" s="1">
-        <v>14</v>
+      <c r="A88" t="n" s="4">
+        <v>4.0</v>
+      </c>
+      <c r="B88" t="s" s="3">
+        <v>61</v>
+      </c>
+      <c r="C88" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D88" t="s" s="3">
+        <v>52</v>
+      </c>
+      <c r="E88" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F88" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s" s="1">
+        <v>33</v>
+      </c>
+      <c r="B89" t="s" s="0">
+        <v>53</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="s" s="1">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="B92" t="s" s="0">
-        <v>61</v>
+        <v>62</v>
+      </c>
+      <c r="C92" t="s" s="1">
+        <v>13</v>
       </c>
       <c r="E92" t="s" s="1">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="s" s="1">
+        <v>15</v>
+      </c>
+      <c r="B93" t="s" s="0">
+        <v>63</v>
+      </c>
+      <c r="E93" t="s" s="1">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="s" s="1">
         <v>18</v>
       </c>
-      <c r="B93" t="s" s="0">
+      <c r="B94" t="s" s="0">
         <v>19</v>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" t="s" s="2">
+    <row r="95">
+      <c r="A95" t="s" s="2">
         <v>20</v>
       </c>
-      <c r="B94" t="s" s="2">
+      <c r="B95" t="s" s="2">
         <v>21</v>
       </c>
-      <c r="C94" t="s" s="2">
+      <c r="C95" t="s" s="2">
         <v>22</v>
       </c>
-      <c r="D94" t="s" s="2">
+      <c r="D95" t="s" s="2">
         <v>23</v>
       </c>
-      <c r="E94" t="s" s="2">
+      <c r="E95" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="F94" t="s" s="2">
+      <c r="F95" t="s" s="2">
         <v>25</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="n" s="4">
-        <v>1.0</v>
-      </c>
-      <c r="B95" t="s" s="3">
-        <v>26</v>
-      </c>
-      <c r="C95" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D95" t="s" s="3">
-        <v>28</v>
-      </c>
-      <c r="E95" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F95" t="s" s="3">
-        <v>27</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n" s="4">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="B96" t="s" s="3">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C96" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D96" t="s" s="3">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E96" t="s" s="3">
         <v>27</v>
@@ -1608,16 +1535,16 @@
     </row>
     <row r="97">
       <c r="A97" t="n" s="4">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="B97" t="s" s="3">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C97" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D97" t="s" s="3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E97" t="s" s="3">
         <v>27</v>
@@ -1628,16 +1555,16 @@
     </row>
     <row r="98">
       <c r="A98" t="n" s="4">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="B98" t="s" s="3">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C98" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D98" t="s" s="3">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="E98" t="s" s="3">
         <v>27</v>
@@ -1648,16 +1575,16 @@
     </row>
     <row r="99">
       <c r="A99" t="n" s="4">
-        <v>5.0</v>
+        <v>4.0</v>
       </c>
       <c r="B99" t="s" s="3">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C99" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D99" t="s" s="3">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="E99" t="s" s="3">
         <v>27</v>
@@ -1668,10 +1595,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="1">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B100" t="s" s="0">
-        <v>51</v>
+        <v>53</v>
       </c>
     </row>
     <row r="103">
@@ -1679,7 +1606,7 @@
         <v>11</v>
       </c>
       <c r="B103" t="s" s="0">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C103" t="s" s="1">
         <v>13</v>
@@ -1693,7 +1620,7 @@
         <v>15</v>
       </c>
       <c r="B104" t="s" s="0">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="E104" t="s" s="1">
         <v>17</v>
@@ -1778,7 +1705,7 @@
         <v>27</v>
       </c>
       <c r="D109" t="s" s="3">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="E109" t="s" s="3">
         <v>27</v>
@@ -1792,114 +1719,114 @@
         <v>4.0</v>
       </c>
       <c r="B110" t="s" s="3">
+        <v>68</v>
+      </c>
+      <c r="C110" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D110" t="s" s="3">
+        <v>52</v>
+      </c>
+      <c r="E110" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F110" t="s" s="3">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="s" s="1">
         <v>33</v>
       </c>
-      <c r="C110" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D110" t="s" s="3">
-        <v>65</v>
-      </c>
-      <c r="E110" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F110" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="n" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="B111" t="s" s="3">
-        <v>66</v>
-      </c>
-      <c r="C111" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D111" t="s" s="3">
-        <v>50</v>
-      </c>
-      <c r="E111" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F111" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="B112" t="s" s="0">
-        <v>51</v>
+      <c r="B111" t="s" s="0">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="s" s="1">
+        <v>11</v>
+      </c>
+      <c r="B114" t="s" s="0">
+        <v>69</v>
+      </c>
+      <c r="C114" t="s" s="1">
+        <v>13</v>
+      </c>
+      <c r="E114" t="s" s="1">
+        <v>14</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="s" s="1">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B115" t="s" s="0">
-        <v>67</v>
-      </c>
-      <c r="C115" t="s" s="1">
-        <v>13</v>
+        <v>70</v>
       </c>
       <c r="E115" t="s" s="1">
-        <v>14</v>
+        <v>17</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="s" s="1">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B116" t="s" s="0">
-        <v>68</v>
-      </c>
-      <c r="E116" t="s" s="1">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="117">
-      <c r="A117" t="s" s="1">
-        <v>18</v>
-      </c>
-      <c r="B117" t="s" s="0">
-        <v>19</v>
+      <c r="A117" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="B117" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="C117" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="D117" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="E117" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="F117" t="s" s="2">
+        <v>25</v>
       </c>
     </row>
     <row r="118">
-      <c r="A118" t="s" s="2">
-        <v>20</v>
-      </c>
-      <c r="B118" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="C118" t="s" s="2">
-        <v>22</v>
-      </c>
-      <c r="D118" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="E118" t="s" s="2">
-        <v>24</v>
-      </c>
-      <c r="F118" t="s" s="2">
-        <v>25</v>
+      <c r="A118" t="n" s="4">
+        <v>1.0</v>
+      </c>
+      <c r="B118" t="s" s="3">
+        <v>26</v>
+      </c>
+      <c r="C118" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="D118" t="s" s="3">
+        <v>28</v>
+      </c>
+      <c r="E118" t="s" s="3">
+        <v>27</v>
+      </c>
+      <c r="F118" t="s" s="3">
+        <v>27</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n" s="4">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
       <c r="B119" t="s" s="3">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="C119" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D119" t="s" s="3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="E119" t="s" s="3">
         <v>27</v>
@@ -1910,16 +1837,16 @@
     </row>
     <row r="120">
       <c r="A120" t="n" s="4">
-        <v>2.0</v>
+        <v>3.0</v>
       </c>
       <c r="B120" t="s" s="3">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="C120" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D120" t="s" s="3">
-        <v>30</v>
+        <v>71</v>
       </c>
       <c r="E120" t="s" s="3">
         <v>27</v>
@@ -1930,16 +1857,16 @@
     </row>
     <row r="121">
       <c r="A121" t="n" s="4">
-        <v>3.0</v>
+        <v>4.0</v>
       </c>
       <c r="B121" t="s" s="3">
-        <v>31</v>
+        <v>72</v>
       </c>
       <c r="C121" t="s" s="3">
         <v>27</v>
       </c>
       <c r="D121" t="s" s="3">
-        <v>32</v>
+        <v>52</v>
       </c>
       <c r="E121" t="s" s="3">
         <v>27</v>
@@ -1949,51 +1876,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" t="n" s="4">
-        <v>4.0</v>
-      </c>
-      <c r="B122" t="s" s="3">
+      <c r="A122" t="s" s="1">
         <v>33</v>
       </c>
-      <c r="C122" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D122" t="s" s="3">
-        <v>69</v>
-      </c>
-      <c r="E122" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F122" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="n" s="4">
-        <v>5.0</v>
-      </c>
-      <c r="B123" t="s" s="3">
-        <v>70</v>
-      </c>
-      <c r="C123" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="D123" t="s" s="3">
-        <v>50</v>
-      </c>
-      <c r="E123" t="s" s="3">
-        <v>27</v>
-      </c>
-      <c r="F123" t="s" s="3">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="s" s="1">
-        <v>35</v>
-      </c>
-      <c r="B124" t="s" s="0">
-        <v>51</v>
+      <c r="B122" t="s" s="0">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
